--- a/cloudflare-deploy/public/library/student/student-en.xlsx
+++ b/cloudflare-deploy/public/library/student/student-en.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2245,87 @@
       <c r="E40" s="15" t="inlineStr">
         <is>
           <t>Listen slowly and repeat clearly to nail the four tones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="54" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>📔</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>AI Voice Diary</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>On the home menu, tap the 📔 AI Voice Diary card (next to the English/Chinese pronunciation coach). → In the 🎤 Record tab, press ‘Start recording’ and talk about your day in English (about 30 seconds is plenty!). → Press ‘Stop’ and AI automatically does transcribe → correct → score &amp; encourage. → The 📅 Calendar tab lets you revisit past entries by date.</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>It doesn't have to be perfect. The habit of saying even ‘one sentence’ a day matters most!</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="54" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>🚀</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Where to next? (Learning-flow guide)</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Fully complete a warm-up, student game, review quiz, class, or step-by-step pronunciation. → Look for the ‘🚀 Choose next activity’ button (or the menu that appears automatically). → Pick from Enter Class · AI Warm-up · Review Quiz · Student Games · Replay Recording · Pronunciation, etc. → The recommended (⭐) item is a good next step for right now.</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>When you're unsure what to do, open this menu to keep today's study flowing smoothly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="54" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Ask the A.i Assistant</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Tap the A.i Assistant icon at the bottom-right of the home screen. → Type your question freely (e.g. “Where do I take the review quiz?”). → The assistant answers and guides you to the right menu. → You can also speak your question using the 🎤 mic.</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>Say what you want to do, like “I want to ○○,” and it takes you to that screen.</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F422"/>
+  <dimension ref="A1:F459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6924,12 +7005,430 @@
       <c r="E422" s="33" t="n"/>
       <c r="F422" s="33" t="n"/>
     </row>
+    <row r="424" ht="26" customHeight="1">
+      <c r="A424" s="21" t="inlineStr">
+        <is>
+          <t>38  📔 AI Voice Diary  —  Speak about your day in English and AI corrects it</t>
+        </is>
+      </c>
+      <c r="B424" s="22" t="n"/>
+      <c r="C424" s="22" t="n"/>
+      <c r="D424" s="22" t="n"/>
+      <c r="E424" s="22" t="n"/>
+      <c r="F424" s="22" t="n"/>
+    </row>
+    <row r="425" ht="42" customHeight="1">
+      <c r="A425" s="23" t="inlineStr">
+        <is>
+          <t>📖 Say what happened today in English, and AI transcribes your speech, polishes the sentences, and leaves a score and encouragement. A little every day builds your own English diary!</t>
+        </is>
+      </c>
+      <c r="B425" s="24" t="n"/>
+      <c r="C425" s="24" t="n"/>
+      <c r="D425" s="24" t="n"/>
+      <c r="E425" s="24" t="n"/>
+      <c r="F425" s="24" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B426" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="30" customHeight="1">
+      <c r="A427" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B427" s="28" t="inlineStr">
+        <is>
+          <t>On the home menu, tap the 📔 AI Voice Diary card (next to the English/Chinese pronunciation coach).</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="30" customHeight="1">
+      <c r="A428" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B428" s="28" t="inlineStr">
+        <is>
+          <t>In the 🎤 Record tab, press ‘Start recording’ and talk about your day in English (about 30 seconds is plenty!).</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="30" customHeight="1">
+      <c r="A429" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B429" s="28" t="inlineStr">
+        <is>
+          <t>Press ‘Stop’ and AI automatically does transcribe → correct → score &amp; encourage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="30" customHeight="1">
+      <c r="A430" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B430" s="28" t="inlineStr">
+        <is>
+          <t>The 📅 Calendar tab lets you revisit past entries by date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="24" customHeight="1">
+      <c r="A431" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B431" s="30" t="inlineStr">
+        <is>
+          <t>Turns your spoken English into text and rewrites awkward sentences naturally.</t>
+        </is>
+      </c>
+      <c r="C431" s="31" t="n"/>
+      <c r="D431" s="31" t="n"/>
+      <c r="E431" s="31" t="n"/>
+      <c r="F431" s="31" t="n"/>
+    </row>
+    <row r="432" ht="24" customHeight="1">
+      <c r="A432" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B432" s="30" t="inlineStr">
+        <is>
+          <t>A score (0–100) and a word of encouragement keep you motivated daily.</t>
+        </is>
+      </c>
+      <c r="C432" s="31" t="n"/>
+      <c r="D432" s="31" t="n"/>
+      <c r="E432" s="31" t="n"/>
+      <c r="F432" s="31" t="n"/>
+    </row>
+    <row r="433" ht="24" customHeight="1">
+      <c r="A433" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B433" s="30" t="inlineStr">
+        <is>
+          <t>Doing it daily also connects to attendance streaks and badges.</t>
+        </is>
+      </c>
+      <c r="C433" s="31" t="n"/>
+      <c r="D433" s="31" t="n"/>
+      <c r="E433" s="31" t="n"/>
+      <c r="F433" s="31" t="n"/>
+    </row>
+    <row r="434" ht="26" customHeight="1">
+      <c r="A434" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Recording requires you to be logged in. Speaking clearly in a quiet place makes the transcription more accurate.</t>
+        </is>
+      </c>
+      <c r="B434" s="35" t="n"/>
+      <c r="C434" s="35" t="n"/>
+      <c r="D434" s="35" t="n"/>
+      <c r="E434" s="35" t="n"/>
+      <c r="F434" s="35" t="n"/>
+    </row>
+    <row r="435" ht="30" customHeight="1">
+      <c r="A435" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · It doesn't have to be perfect. The habit of saying even ‘one sentence’ a day matters most!</t>
+        </is>
+      </c>
+      <c r="B435" s="33" t="n"/>
+      <c r="C435" s="33" t="n"/>
+      <c r="D435" s="33" t="n"/>
+      <c r="E435" s="33" t="n"/>
+      <c r="F435" s="33" t="n"/>
+    </row>
+    <row r="437" ht="26" customHeight="1">
+      <c r="A437" s="21" t="inlineStr">
+        <is>
+          <t>39  🚀 Where to next? (Learning-flow guide)  —  Finish one activity and get the next one suggested</t>
+        </is>
+      </c>
+      <c r="B437" s="22" t="n"/>
+      <c r="C437" s="22" t="n"/>
+      <c r="D437" s="22" t="n"/>
+      <c r="E437" s="22" t="n"/>
+      <c r="F437" s="22" t="n"/>
+    </row>
+    <row r="438" ht="42" customHeight="1">
+      <c r="A438" s="23" t="inlineStr">
+        <is>
+          <t>📖 When you finish an activity — warm-up, game, class, review, pronunciation — a ‘🚀 Where would you like to go next?’ menu pops up. No need to hunt for menus again; just follow the recommended (⭐) item to flow into your next activity.</t>
+        </is>
+      </c>
+      <c r="B438" s="24" t="n"/>
+      <c r="C438" s="24" t="n"/>
+      <c r="D438" s="24" t="n"/>
+      <c r="E438" s="24" t="n"/>
+      <c r="F438" s="24" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B439" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="30" customHeight="1">
+      <c r="A440" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B440" s="28" t="inlineStr">
+        <is>
+          <t>Fully complete a warm-up, student game, review quiz, class, or step-by-step pronunciation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="30" customHeight="1">
+      <c r="A441" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B441" s="28" t="inlineStr">
+        <is>
+          <t>Look for the ‘🚀 Choose next activity’ button (or the menu that appears automatically).</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="30" customHeight="1">
+      <c r="A442" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B442" s="28" t="inlineStr">
+        <is>
+          <t>Pick from Enter Class · AI Warm-up · Review Quiz · Student Games · Replay Recording · Pronunciation, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="30" customHeight="1">
+      <c r="A443" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B443" s="28" t="inlineStr">
+        <is>
+          <t>The recommended (⭐) item is a good next step for right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="24" customHeight="1">
+      <c r="A444" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B444" s="30" t="inlineStr">
+        <is>
+          <t>Suggested flow: Warm-up → Game → Class → Review → Pronunciation → Game, naturally connected.</t>
+        </is>
+      </c>
+      <c r="C444" s="31" t="n"/>
+      <c r="D444" s="31" t="n"/>
+      <c r="E444" s="31" t="n"/>
+      <c r="F444" s="31" t="n"/>
+    </row>
+    <row r="445" ht="24" customHeight="1">
+      <c r="A445" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B445" s="30" t="inlineStr">
+        <is>
+          <t>Choosing ‘Replay Recording’ instantly replays your last class video.</t>
+        </is>
+      </c>
+      <c r="C445" s="31" t="n"/>
+      <c r="D445" s="31" t="n"/>
+      <c r="E445" s="31" t="n"/>
+      <c r="F445" s="31" t="n"/>
+    </row>
+    <row r="446" ht="24" customHeight="1">
+      <c r="A446" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B446" s="30" t="inlineStr">
+        <is>
+          <t>Even without playing a game/quiz, the list screen's ‘🚀 Go next’ button opens the menu.</t>
+        </is>
+      </c>
+      <c r="C446" s="31" t="n"/>
+      <c r="D446" s="31" t="n"/>
+      <c r="E446" s="31" t="n"/>
+      <c r="F446" s="31" t="n"/>
+    </row>
+    <row r="447" ht="30" customHeight="1">
+      <c r="A447" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · When you're unsure what to do, open this menu to keep today's study flowing smoothly.</t>
+        </is>
+      </c>
+      <c r="B447" s="33" t="n"/>
+      <c r="C447" s="33" t="n"/>
+      <c r="D447" s="33" t="n"/>
+      <c r="E447" s="33" t="n"/>
+      <c r="F447" s="33" t="n"/>
+    </row>
+    <row r="449" ht="26" customHeight="1">
+      <c r="A449" s="21" t="inlineStr">
+        <is>
+          <t>40  🤖 Ask the A.i Assistant  —  The consultant avatar at the bottom-right</t>
+        </is>
+      </c>
+      <c r="B449" s="22" t="n"/>
+      <c r="C449" s="22" t="n"/>
+      <c r="D449" s="22" t="n"/>
+      <c r="E449" s="22" t="n"/>
+      <c r="F449" s="22" t="n"/>
+    </row>
+    <row r="450" ht="42" customHeight="1">
+      <c r="A450" s="23" t="inlineStr">
+        <is>
+          <t>📖 Tap the ‘A.i Assistant’ at the bottom-right of the screen to ask anything, anytime. It explains how to use features and where they are, and can take you straight to the right menu.</t>
+        </is>
+      </c>
+      <c r="B450" s="24" t="n"/>
+      <c r="C450" s="24" t="n"/>
+      <c r="D450" s="24" t="n"/>
+      <c r="E450" s="24" t="n"/>
+      <c r="F450" s="24" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B451" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="30" customHeight="1">
+      <c r="A452" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B452" s="28" t="inlineStr">
+        <is>
+          <t>Tap the A.i Assistant icon at the bottom-right of the home screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="30" customHeight="1">
+      <c r="A453" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B453" s="28" t="inlineStr">
+        <is>
+          <t>Type your question freely (e.g. “Where do I take the review quiz?”).</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="30" customHeight="1">
+      <c r="A454" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B454" s="28" t="inlineStr">
+        <is>
+          <t>The assistant answers and guides you to the right menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="30" customHeight="1">
+      <c r="A455" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B455" s="28" t="inlineStr">
+        <is>
+          <t>You can also speak your question using the 🎤 mic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="24" customHeight="1">
+      <c r="A456" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B456" s="30" t="inlineStr">
+        <is>
+          <t>Points you straight to features like student games, pronunciation coach, or voice diary.</t>
+        </is>
+      </c>
+      <c r="C456" s="31" t="n"/>
+      <c r="D456" s="31" t="n"/>
+      <c r="E456" s="31" t="n"/>
+      <c r="F456" s="31" t="n"/>
+    </row>
+    <row r="457" ht="24" customHeight="1">
+      <c r="A457" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B457" s="30" t="inlineStr">
+        <is>
+          <t>Available anytime (nights &amp; weekends too) so you can use everything on your own.</t>
+        </is>
+      </c>
+      <c r="C457" s="31" t="n"/>
+      <c r="D457" s="31" t="n"/>
+      <c r="E457" s="31" t="n"/>
+      <c r="F457" s="31" t="n"/>
+    </row>
+    <row r="458" ht="26" customHeight="1">
+      <c r="A458" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Requests that need a human — billing, operations — are routed to KakaoTalk chat or customer support.</t>
+        </is>
+      </c>
+      <c r="B458" s="35" t="n"/>
+      <c r="C458" s="35" t="n"/>
+      <c r="D458" s="35" t="n"/>
+      <c r="E458" s="35" t="n"/>
+      <c r="F458" s="35" t="n"/>
+    </row>
+    <row r="459" ht="30" customHeight="1">
+      <c r="A459" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Say what you want to do, like “I want to ○○,” and it takes you to that screen.</t>
+        </is>
+      </c>
+      <c r="B459" s="33" t="n"/>
+      <c r="C459" s="33" t="n"/>
+      <c r="D459" s="33" t="n"/>
+      <c r="E459" s="33" t="n"/>
+      <c r="F459" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="385">
+  <mergeCells count="419">
     <mergeCell ref="A183:F183"/>
     <mergeCell ref="B209:F209"/>
+    <mergeCell ref="B445:F445"/>
     <mergeCell ref="B301:F301"/>
     <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B432:F432"/>
     <mergeCell ref="B276:F276"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B238:F238"/>
@@ -6949,17 +7448,22 @@
     <mergeCell ref="B368:F368"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B433:F433"/>
     <mergeCell ref="A252:F252"/>
     <mergeCell ref="B227:F227"/>
     <mergeCell ref="B420:F420"/>
     <mergeCell ref="B199:F199"/>
     <mergeCell ref="B370:F370"/>
+    <mergeCell ref="A438:F438"/>
     <mergeCell ref="B291:F291"/>
+    <mergeCell ref="A425:F425"/>
     <mergeCell ref="B228:F228"/>
     <mergeCell ref="A262:F262"/>
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="B148:F148"/>
+    <mergeCell ref="B446:F446"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A435:F435"/>
     <mergeCell ref="A362:F362"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B146:F146"/>
@@ -6970,12 +7474,14 @@
     <mergeCell ref="B383:F383"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A413:F413"/>
+    <mergeCell ref="B439:F439"/>
     <mergeCell ref="A375:F375"/>
     <mergeCell ref="B159:F159"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A154:F154"/>
     <mergeCell ref="A390:F390"/>
     <mergeCell ref="A129:F129"/>
+    <mergeCell ref="B441:F441"/>
     <mergeCell ref="B161:F161"/>
     <mergeCell ref="B259:F259"/>
     <mergeCell ref="B136:F136"/>
@@ -6989,6 +7495,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B91:F91"/>
     <mergeCell ref="B327:F327"/>
+    <mergeCell ref="B454:F454"/>
     <mergeCell ref="A365:F365"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B93:F93"/>
@@ -7008,9 +7515,11 @@
     <mergeCell ref="A155:F155"/>
     <mergeCell ref="B246:F246"/>
     <mergeCell ref="B40:F40"/>
+    <mergeCell ref="A437:F437"/>
     <mergeCell ref="B338:F338"/>
     <mergeCell ref="A284:F284"/>
     <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B444:F444"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B340:F340"/>
     <mergeCell ref="B79:F79"/>
@@ -7024,11 +7533,14 @@
     <mergeCell ref="A386:F386"/>
     <mergeCell ref="A373:F373"/>
     <mergeCell ref="B328:F328"/>
+    <mergeCell ref="B455:F455"/>
+    <mergeCell ref="A450:F450"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B270:F270"/>
     <mergeCell ref="B392:F392"/>
     <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B457:F457"/>
     <mergeCell ref="B257:F257"/>
     <mergeCell ref="B288:F288"/>
     <mergeCell ref="B92:F92"/>
@@ -7053,6 +7565,7 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A412:F412"/>
     <mergeCell ref="A387:F387"/>
+    <mergeCell ref="A458:F458"/>
     <mergeCell ref="B359:F359"/>
     <mergeCell ref="B207:F207"/>
     <mergeCell ref="B204:F204"/>
@@ -7066,6 +7579,7 @@
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A242:F242"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B443:F443"/>
     <mergeCell ref="A244:F244"/>
     <mergeCell ref="A171:F171"/>
     <mergeCell ref="A342:F342"/>
@@ -7075,10 +7589,12 @@
     <mergeCell ref="B349:F349"/>
     <mergeCell ref="A344:F344"/>
     <mergeCell ref="A400:F400"/>
+    <mergeCell ref="B426:F426"/>
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A245:F245"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="A402:F402"/>
+    <mergeCell ref="B428:F428"/>
     <mergeCell ref="B415:F415"/>
     <mergeCell ref="A168:F168"/>
     <mergeCell ref="B63:F63"/>
@@ -7111,9 +7627,11 @@
     <mergeCell ref="B236:F236"/>
     <mergeCell ref="B307:F307"/>
     <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B429:F429"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B350:F350"/>
     <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B431:F431"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B287:F287"/>
     <mergeCell ref="B358:F358"/>
@@ -7130,12 +7648,17 @@
     <mergeCell ref="B378:F378"/>
     <mergeCell ref="A422:F422"/>
     <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B442:F442"/>
     <mergeCell ref="A335:F335"/>
     <mergeCell ref="B208:F208"/>
+    <mergeCell ref="A447:F447"/>
+    <mergeCell ref="A434:F434"/>
     <mergeCell ref="B219:F219"/>
     <mergeCell ref="A213:F213"/>
     <mergeCell ref="B210:F210"/>
+    <mergeCell ref="A449:F449"/>
     <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A424:F424"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B318:F318"/>
     <mergeCell ref="A190:F190"/>
@@ -7163,9 +7686,12 @@
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="A140:F140"/>
+    <mergeCell ref="B452:F452"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="B258:F258"/>
     <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B451:F451"/>
+    <mergeCell ref="B456:F456"/>
     <mergeCell ref="B260:F260"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="B36:F36"/>
@@ -7186,6 +7712,7 @@
     <mergeCell ref="A376:F376"/>
     <mergeCell ref="B102:F102"/>
     <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B440:F440"/>
     <mergeCell ref="B240:F240"/>
     <mergeCell ref="A234:F234"/>
     <mergeCell ref="B377:F377"/>
@@ -7199,6 +7726,7 @@
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="B393:F393"/>
     <mergeCell ref="B331:F331"/>
+    <mergeCell ref="B453:F453"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B197:F197"/>
@@ -7218,6 +7746,7 @@
     <mergeCell ref="B166:F166"/>
     <mergeCell ref="B408:F408"/>
     <mergeCell ref="A332:F332"/>
+    <mergeCell ref="A459:F459"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B174:F174"/>
     <mergeCell ref="B108:F108"/>
@@ -7295,6 +7824,7 @@
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B430:F430"/>
     <mergeCell ref="B119:F119"/>
     <mergeCell ref="B290:F290"/>
     <mergeCell ref="A43:F43"/>
@@ -7302,6 +7832,7 @@
     <mergeCell ref="A170:F170"/>
     <mergeCell ref="B196:F196"/>
     <mergeCell ref="B367:F367"/>
+    <mergeCell ref="B427:F427"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B348:F348"/>
     <mergeCell ref="B419:F419"/>

--- a/cloudflare-deploy/public/library/student/student-en.xlsx
+++ b/cloudflare-deploy/public/library/student/student-en.xlsx
@@ -1108,7 +1108,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>🌐 test.mangoi.co.kr    📞 1588-0000    ✉ support@mangoi.co.kr</t>
+          <t>🌐 www.mangoi.co.kr    📞 1644-0561    ✉ support@mangoi.co.kr</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>Go to test.mangoi.co.kr in your browser and log in (social login works too). → Check your name and points (P) at the top-right to confirm you're logged in. → Tap the 'Open' tab on the left to expand the menu sidebar. → Ask the A.i assistant at the bottom-right anything you're curious about. → Use the EN button to switch the on-screen text to English.</t>
+          <t>Go to www.mangoi.co.kr in your browser and log in (social login works too). → Check your name and points (P) at the top-right to confirm you're logged in. → Tap the 'Open' tab on the left to expand the menu sidebar. → Ask the A.i assistant at the bottom-right anything you're curious about. → Use the EN button to switch the on-screen text to English.</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B6" s="28" t="inlineStr">
         <is>
-          <t>Go to test.mangoi.co.kr in your browser and log in (social login works too).</t>
+          <t>Go to www.mangoi.co.kr in your browser and log in (social login works too).</t>
         </is>
       </c>
     </row>

--- a/cloudflare-deploy/public/library/student/student-en.xlsx
+++ b/cloudflare-deploy/public/library/student/student-en.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2326,6 +2326,87 @@
       <c r="E43" s="20" t="inlineStr">
         <is>
           <t>Say what you want to do, like “I want to ○○,” and it takes you to that screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="54" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>🎛️</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>New Classroom Comforts</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>Tap the 🙈 button on your own tile to hide your face for a bit. Tap the 🙂 chip to bring it back. → When you enter, the teacher's face is placed on top, large, automatically — no hunting. → On a phone (portrait), the default screen is faces on top and the textbook below. → The mobile bottom dock opens only when you tap ⋯, keeping the screen roomy.</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>If the screen feels cramped, fold the dock away with the ⋯ button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="54" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>💬</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>1:1 Private Chat &amp; File Sharing</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Open 💬 Chat from the bottom dock. → Switch the recipient from Everyone to a teacher's name to whisper 1:1. → Use the 📎 file button to upload a PDF, photo, or document — a download card appears for them. → Received files are saved with the card's ⬇ Save button.</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>Perfect for quietly asking a question without interrupting anyone else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="54" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>🌗</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>Home Screen: Bright · Dark</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Find the 🌗 theme chip at the top of the home screen. → Pick Bright · Auto · Dark. → Leave it on Auto and it brightens in the morning and dims at night on its own.</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Dark for bedtime review, bright for a morning warm-up — it changes the mood too!</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F459"/>
+  <dimension ref="A1:F493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7421,8 +7502,382 @@
       <c r="E459" s="33" t="n"/>
       <c r="F459" s="33" t="n"/>
     </row>
+    <row r="461" ht="26" customHeight="1">
+      <c r="A461" s="21" t="inlineStr">
+        <is>
+          <t>41  🎛️ New Classroom Comforts  —  Hide my face · teacher first · mobile tool dock</t>
+        </is>
+      </c>
+      <c r="B461" s="22" t="n"/>
+      <c r="C461" s="22" t="n"/>
+      <c r="D461" s="22" t="n"/>
+      <c r="E461" s="22" t="n"/>
+      <c r="F461" s="22" t="n"/>
+    </row>
+    <row r="462" ht="42" customHeight="1">
+      <c r="A462" s="23" t="inlineStr">
+        <is>
+          <t>📖 The lesson screen got more comfortable. A 🙈 button hides your own face for a moment, the teacher's face now appears first and large when you enter, and on phones the bottom tools stay tucked away behind a ⋯ button — so you can focus on the lesson itself.</t>
+        </is>
+      </c>
+      <c r="B462" s="24" t="n"/>
+      <c r="C462" s="24" t="n"/>
+      <c r="D462" s="24" t="n"/>
+      <c r="E462" s="24" t="n"/>
+      <c r="F462" s="24" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B463" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="30" customHeight="1">
+      <c r="A464" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B464" s="28" t="inlineStr">
+        <is>
+          <t>Tap the 🙈 button on your own tile to hide your face for a bit. Tap the 🙂 chip to bring it back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="30" customHeight="1">
+      <c r="A465" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B465" s="28" t="inlineStr">
+        <is>
+          <t>When you enter, the teacher's face is placed on top, large, automatically — no hunting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="30" customHeight="1">
+      <c r="A466" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B466" s="28" t="inlineStr">
+        <is>
+          <t>On a phone (portrait), the default screen is faces on top and the textbook below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="30" customHeight="1">
+      <c r="A467" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B467" s="28" t="inlineStr">
+        <is>
+          <t>The mobile bottom dock opens only when you tap ⋯, keeping the screen roomy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="24" customHeight="1">
+      <c r="A468" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B468" s="30" t="inlineStr">
+        <is>
+          <t>Hiding your face doesn't turn the camera off — it only hides it on screen, so class continues.</t>
+        </is>
+      </c>
+      <c r="C468" s="31" t="n"/>
+      <c r="D468" s="31" t="n"/>
+      <c r="E468" s="31" t="n"/>
+      <c r="F468" s="31" t="n"/>
+    </row>
+    <row r="469" ht="24" customHeight="1">
+      <c r="A469" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B469" s="30" t="inlineStr">
+        <is>
+          <t>Rotate to landscape and it auto-arranges to faces left · textbook right.</t>
+        </is>
+      </c>
+      <c r="C469" s="31" t="n"/>
+      <c r="D469" s="31" t="n"/>
+      <c r="E469" s="31" t="n"/>
+      <c r="F469" s="31" t="n"/>
+    </row>
+    <row r="470" ht="26" customHeight="1">
+      <c r="A470" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Hide your face only for a moment when you're shy — lessons are much more fun with eye contact!</t>
+        </is>
+      </c>
+      <c r="B470" s="35" t="n"/>
+      <c r="C470" s="35" t="n"/>
+      <c r="D470" s="35" t="n"/>
+      <c r="E470" s="35" t="n"/>
+      <c r="F470" s="35" t="n"/>
+    </row>
+    <row r="471" ht="30" customHeight="1">
+      <c r="A471" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · If the screen feels cramped, fold the dock away with the ⋯ button.</t>
+        </is>
+      </c>
+      <c r="B471" s="33" t="n"/>
+      <c r="C471" s="33" t="n"/>
+      <c r="D471" s="33" t="n"/>
+      <c r="E471" s="33" t="n"/>
+      <c r="F471" s="33" t="n"/>
+    </row>
+    <row r="473" ht="26" customHeight="1">
+      <c r="A473" s="21" t="inlineStr">
+        <is>
+          <t>42  💬 1:1 Private Chat &amp; File Sharing  —  Whisper messages only your teacher sees + share any file</t>
+        </is>
+      </c>
+      <c r="B473" s="22" t="n"/>
+      <c r="C473" s="22" t="n"/>
+      <c r="D473" s="22" t="n"/>
+      <c r="E473" s="22" t="n"/>
+      <c r="F473" s="22" t="n"/>
+    </row>
+    <row r="474" ht="42" customHeight="1">
+      <c r="A474" s="23" t="inlineStr">
+        <is>
+          <t>📖 Class chat now supports 1:1 private messages (DM). Send a message only a specific teacher can see, and share any file — PDF, image, document — through chat; it appears on the other side as a download card.</t>
+        </is>
+      </c>
+      <c r="B474" s="24" t="n"/>
+      <c r="C474" s="24" t="n"/>
+      <c r="D474" s="24" t="n"/>
+      <c r="E474" s="24" t="n"/>
+      <c r="F474" s="24" t="n"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B475" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="30" customHeight="1">
+      <c r="A476" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B476" s="28" t="inlineStr">
+        <is>
+          <t>Open 💬 Chat from the bottom dock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="30" customHeight="1">
+      <c r="A477" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B477" s="28" t="inlineStr">
+        <is>
+          <t>Switch the recipient from Everyone to a teacher's name to whisper 1:1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="30" customHeight="1">
+      <c r="A478" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B478" s="28" t="inlineStr">
+        <is>
+          <t>Use the 📎 file button to upload a PDF, photo, or document — a download card appears for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="30" customHeight="1">
+      <c r="A479" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B479" s="28" t="inlineStr">
+        <is>
+          <t>Received files are saved with the card's ⬇ Save button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="24" customHeight="1">
+      <c r="A480" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B480" s="30" t="inlineStr">
+        <is>
+          <t>Private chats are visible only to the two of you.</t>
+        </is>
+      </c>
+      <c r="C480" s="31" t="n"/>
+      <c r="D480" s="31" t="n"/>
+      <c r="E480" s="31" t="n"/>
+      <c r="F480" s="31" t="n"/>
+    </row>
+    <row r="481" ht="24" customHeight="1">
+      <c r="A481" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B481" s="30" t="inlineStr">
+        <is>
+          <t>Homework files and notes get exchanged in one step during class.</t>
+        </is>
+      </c>
+      <c r="C481" s="31" t="n"/>
+      <c r="D481" s="31" t="n"/>
+      <c r="E481" s="31" t="n"/>
+      <c r="F481" s="31" t="n"/>
+    </row>
+    <row r="482" ht="26" customHeight="1">
+      <c r="A482" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Private chats are not stored on the server and disappear after class. Keep important things as files.</t>
+        </is>
+      </c>
+      <c r="B482" s="35" t="n"/>
+      <c r="C482" s="35" t="n"/>
+      <c r="D482" s="35" t="n"/>
+      <c r="E482" s="35" t="n"/>
+      <c r="F482" s="35" t="n"/>
+    </row>
+    <row r="483" ht="30" customHeight="1">
+      <c r="A483" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Perfect for quietly asking a question without interrupting anyone else.</t>
+        </is>
+      </c>
+      <c r="B483" s="33" t="n"/>
+      <c r="C483" s="33" t="n"/>
+      <c r="D483" s="33" t="n"/>
+      <c r="E483" s="33" t="n"/>
+      <c r="F483" s="33" t="n"/>
+    </row>
+    <row r="485" ht="26" customHeight="1">
+      <c r="A485" s="21" t="inlineStr">
+        <is>
+          <t>43  🌗 Home Screen: Bright · Dark  —  Auto by time of day, or pick your own</t>
+        </is>
+      </c>
+      <c r="B485" s="22" t="n"/>
+      <c r="C485" s="22" t="n"/>
+      <c r="D485" s="22" t="n"/>
+      <c r="E485" s="22" t="n"/>
+      <c r="F485" s="22" t="n"/>
+    </row>
+    <row r="486" ht="42" customHeight="1">
+      <c r="A486" s="23" t="inlineStr">
+        <is>
+          <t>📖 The home screen now switches automatically — bright by day, dark at night. Or use the Bright / Auto / Dark 3-way chip to set the mood yourself, anytime.</t>
+        </is>
+      </c>
+      <c r="B486" s="24" t="n"/>
+      <c r="C486" s="24" t="n"/>
+      <c r="D486" s="24" t="n"/>
+      <c r="E486" s="24" t="n"/>
+      <c r="F486" s="24" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B487" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="30" customHeight="1">
+      <c r="A488" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B488" s="28" t="inlineStr">
+        <is>
+          <t>Find the 🌗 theme chip at the top of the home screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="30" customHeight="1">
+      <c r="A489" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B489" s="28" t="inlineStr">
+        <is>
+          <t>Pick Bright · Auto · Dark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="30" customHeight="1">
+      <c r="A490" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B490" s="28" t="inlineStr">
+        <is>
+          <t>Leave it on Auto and it brightens in the morning and dims at night on its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="24" customHeight="1">
+      <c r="A491" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B491" s="30" t="inlineStr">
+        <is>
+          <t>Late-night studying is easier on the eyes.</t>
+        </is>
+      </c>
+      <c r="C491" s="31" t="n"/>
+      <c r="D491" s="31" t="n"/>
+      <c r="E491" s="31" t="n"/>
+      <c r="F491" s="31" t="n"/>
+    </row>
+    <row r="492" ht="24" customHeight="1">
+      <c r="A492" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B492" s="30" t="inlineStr">
+        <is>
+          <t>Your chosen theme is remembered next time you sign in.</t>
+        </is>
+      </c>
+      <c r="C492" s="31" t="n"/>
+      <c r="D492" s="31" t="n"/>
+      <c r="E492" s="31" t="n"/>
+      <c r="F492" s="31" t="n"/>
+    </row>
+    <row r="493" ht="30" customHeight="1">
+      <c r="A493" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Dark for bedtime review, bright for a morning warm-up — it changes the mood too!</t>
+        </is>
+      </c>
+      <c r="B493" s="33" t="n"/>
+      <c r="C493" s="33" t="n"/>
+      <c r="D493" s="33" t="n"/>
+      <c r="E493" s="33" t="n"/>
+      <c r="F493" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="419">
+  <mergeCells count="450">
     <mergeCell ref="A183:F183"/>
     <mergeCell ref="B209:F209"/>
     <mergeCell ref="B445:F445"/>
@@ -7445,6 +7900,8 @@
     <mergeCell ref="A315:F315"/>
     <mergeCell ref="B356:F356"/>
     <mergeCell ref="B160:F160"/>
+    <mergeCell ref="A486:F486"/>
+    <mergeCell ref="B489:F489"/>
     <mergeCell ref="B368:F368"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B306:F306"/>
@@ -7471,6 +7928,7 @@
     <mergeCell ref="B217:F217"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="B319:F319"/>
+    <mergeCell ref="B490:F490"/>
     <mergeCell ref="B383:F383"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A413:F413"/>
@@ -7513,10 +7971,12 @@
     <mergeCell ref="A389:F389"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="A155:F155"/>
+    <mergeCell ref="B467:F467"/>
     <mergeCell ref="B246:F246"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A437:F437"/>
     <mergeCell ref="B338:F338"/>
+    <mergeCell ref="B469:F469"/>
     <mergeCell ref="A284:F284"/>
     <mergeCell ref="B177:F177"/>
     <mergeCell ref="B444:F444"/>
@@ -7531,10 +7991,12 @@
     <mergeCell ref="B366:F366"/>
     <mergeCell ref="B381:F381"/>
     <mergeCell ref="A386:F386"/>
+    <mergeCell ref="B480:F480"/>
     <mergeCell ref="A373:F373"/>
     <mergeCell ref="B328:F328"/>
     <mergeCell ref="B455:F455"/>
     <mergeCell ref="A450:F450"/>
+    <mergeCell ref="B491:F491"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B270:F270"/>
@@ -7545,6 +8007,7 @@
     <mergeCell ref="B288:F288"/>
     <mergeCell ref="B92:F92"/>
     <mergeCell ref="B394:F394"/>
+    <mergeCell ref="A462:F462"/>
     <mergeCell ref="A399:F399"/>
     <mergeCell ref="A355:F355"/>
     <mergeCell ref="A305:F305"/>
@@ -7553,10 +8016,12 @@
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B185:F185"/>
     <mergeCell ref="A223:F223"/>
+    <mergeCell ref="B475:F475"/>
     <mergeCell ref="A294:F294"/>
     <mergeCell ref="B176:F176"/>
     <mergeCell ref="B347:F347"/>
     <mergeCell ref="B341:F341"/>
+    <mergeCell ref="B468:F468"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="A254:F254"/>
     <mergeCell ref="B405:F405"/>
@@ -7564,6 +8029,7 @@
     <mergeCell ref="A314:F314"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A412:F412"/>
+    <mergeCell ref="B463:F463"/>
     <mergeCell ref="A387:F387"/>
     <mergeCell ref="A458:F458"/>
     <mergeCell ref="B359:F359"/>
@@ -7587,11 +8053,14 @@
     <mergeCell ref="A115:F115"/>
     <mergeCell ref="B178:F178"/>
     <mergeCell ref="B349:F349"/>
+    <mergeCell ref="B476:F476"/>
     <mergeCell ref="A344:F344"/>
     <mergeCell ref="A400:F400"/>
+    <mergeCell ref="A471:F471"/>
     <mergeCell ref="B426:F426"/>
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A245:F245"/>
+    <mergeCell ref="B478:F478"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="A402:F402"/>
     <mergeCell ref="B428:F428"/>
@@ -7602,6 +8071,7 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B286:F286"/>
+    <mergeCell ref="B479:F479"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A255:F255"/>
     <mergeCell ref="A364:F364"/>
@@ -7618,17 +8088,21 @@
     <mergeCell ref="B205:F205"/>
     <mergeCell ref="B339:F339"/>
     <mergeCell ref="A352:F352"/>
+    <mergeCell ref="A485:F485"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A410:F410"/>
     <mergeCell ref="B194:F194"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="A118:F118"/>
+    <mergeCell ref="B492:F492"/>
+    <mergeCell ref="A474:F474"/>
     <mergeCell ref="B131:F131"/>
     <mergeCell ref="B236:F236"/>
     <mergeCell ref="B307:F307"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B429:F429"/>
     <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B465:F465"/>
     <mergeCell ref="B350:F350"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B431:F431"/>
@@ -7661,6 +8135,7 @@
     <mergeCell ref="A424:F424"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B318:F318"/>
+    <mergeCell ref="A482:F482"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B308:F308"/>
@@ -7674,6 +8149,7 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B361:F361"/>
+    <mergeCell ref="A493:F493"/>
     <mergeCell ref="B150:F150"/>
     <mergeCell ref="B321:F321"/>
     <mergeCell ref="B215:F215"/>
@@ -7691,6 +8167,7 @@
     <mergeCell ref="B258:F258"/>
     <mergeCell ref="B147:F147"/>
     <mergeCell ref="B451:F451"/>
+    <mergeCell ref="B481:F481"/>
     <mergeCell ref="B456:F456"/>
     <mergeCell ref="B260:F260"/>
     <mergeCell ref="A94:F94"/>
@@ -7745,6 +8222,7 @@
     <mergeCell ref="B250:F250"/>
     <mergeCell ref="B166:F166"/>
     <mergeCell ref="B408:F408"/>
+    <mergeCell ref="B464:F464"/>
     <mergeCell ref="A332:F332"/>
     <mergeCell ref="A459:F459"/>
     <mergeCell ref="B37:F37"/>
@@ -7752,9 +8230,12 @@
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B230:F230"/>
     <mergeCell ref="B279:F279"/>
+    <mergeCell ref="B466:F466"/>
+    <mergeCell ref="B477:F477"/>
     <mergeCell ref="B281:F281"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B256:F256"/>
+    <mergeCell ref="A473:F473"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B134:F134"/>
@@ -7779,10 +8260,12 @@
     <mergeCell ref="A182:F182"/>
     <mergeCell ref="A304:F304"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="A461:F461"/>
     <mergeCell ref="B251:F251"/>
     <mergeCell ref="B189:F189"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B216:F216"/>
+    <mergeCell ref="B487:F487"/>
     <mergeCell ref="B414:F414"/>
     <mergeCell ref="B188:F188"/>
     <mergeCell ref="B109:F109"/>
@@ -7793,6 +8276,7 @@
     <mergeCell ref="B416:F416"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B488:F488"/>
     <mergeCell ref="A179:F179"/>
     <mergeCell ref="B409:F409"/>
     <mergeCell ref="A322:F322"/>
@@ -7820,8 +8304,10 @@
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A312:F312"/>
+    <mergeCell ref="A483:F483"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="B67:F67"/>
+    <mergeCell ref="A470:F470"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B430:F430"/>

--- a/cloudflare-deploy/public/library/student/student-en.xlsx
+++ b/cloudflare-deploy/public/library/student/student-en.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2407,6 +2407,195 @@
       <c r="E46" s="15" t="inlineStr">
         <is>
           <t>Dark for bedtime review, bright for a morning warm-up — it changes the mood too!</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="54" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Judgment Training (pick the right words)</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>On the student home, open AI Learning Tools → 🧠 Judgment Training. → Read Here's the situation and pick one of A–D. → In Why did you choose it?, write your reason. Your own language is fine. → Press Submit — the AI scores it and explains why another option may fit better. → Tap 🏅 My Growth (top right) to see your judgment index and its 5 axes.</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>Getting it wrong is fine. Writing why you thought so is the whole point of this training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="54" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>🍕</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Grammar Pizza Master (word order)</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Open 🍕 Grammar Pizza Master in the games hub. → Press Listen and start to hear the sentence first. → Place the toppings below in sentence order onto the pizza. → Stuck? Tap 💡 Hint! at the top right. → Sentences grow longer from Level 1 → 2 → 3.</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>Read each word aloud as you place it — the order sticks far faster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="54" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>🧱</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>Word Tetris</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Open 🧱 Word Tetris in the games hub. → Choose US English mode or CN Chinese mode. → Use ◀ ▶ to move, rotate, ▼ to speed up, ↓ to drop instantly. → Each time a block lands you hear the word — repeat it aloud.</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>Lay the long words down low first — clearing lines gets much easier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="54" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>Tank Battle · Language Ace</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Open 🛡️ Tank Battle or ✈️ Language Ace in the games hub. → For Tank Battle pick English / 中文, a battlefield (grass · desert · snow) and difficulty 1–7. → Hold and drag the left button to move; short tap fires in that direction. → Destroy the tanks carrying the gold words of the sentence above, in order. → Pick up jelly fuel cans to gain more time.</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>Games work best as review after the lesson, not before it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="54" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>🔐</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Log in with your face or fingerprint (passkey)</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>Update the app to the latest version (v1.9 or later). → Log in once with your ID and password as usual. → When prompted, tap Register passkey and enrol your face or fingerprint. → From then on, log in with your face or fingerprint.</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>Younger students forget passwords constantly. Registering a passkey cuts those requests dramatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="54" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🎤</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>Your speaking isn't cut off any more · a smarter AI friend</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>Press the 🎤 button in Speech Coach, AI Warm-up or AI Friend and talk. → Pausing to think is fine — it waits until you're really finished. → Say “Please speak slowly” to the AI friend and it will slow down. → Choose the voice: male · female · alternating.</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>Using an earphone microphone raises recognition accuracy noticeably.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="54" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>💳</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>Enrol and pay in one go</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>Open the Enrolment screen. → ① Choose a teacher. → ② Lesson options — times per week (1–5), term (1 / 3 / 6 / 12 months), length (20 or 40 min). → ③ Days &amp; time — pick as many days as your weekly count, then the start time and start date. → When ✅ Available appears, press Pay at the bottom. → Once payment completes, every session is created at once. Check it on My Page.</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>Avoid days with school commitments. Choosing well up front beats rescheduling later.</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F493"/>
+  <dimension ref="A1:F588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7876,25 +8065,1112 @@
       <c r="E493" s="33" t="n"/>
       <c r="F493" s="33" t="n"/>
     </row>
+    <row r="495" ht="26" customHeight="1">
+      <c r="A495" s="21" t="inlineStr">
+        <is>
+          <t>44  🧠 Judgment Training (pick the right words)  —  Not memorising answers — what fits right now?</t>
+        </is>
+      </c>
+      <c r="B495" s="22" t="n"/>
+      <c r="C495" s="22" t="n"/>
+      <c r="D495" s="22" t="n"/>
+      <c r="E495" s="22" t="n"/>
+      <c r="F495" s="22" t="n"/>
+    </row>
+    <row r="496" ht="42" customHeight="1">
+      <c r="A496" s="23" t="inlineStr">
+        <is>
+          <t>📖 The AI creates a situation that could really happen, and you pick the expression that fits that situation best — then write one line saying why you chose it. “Give me that!” works with a friend, but “Could I have that, please?” is right for a teacher. Real English ability isn't how much you know; it's judging which words fit right now.</t>
+        </is>
+      </c>
+      <c r="B496" s="24" t="n"/>
+      <c r="C496" s="24" t="n"/>
+      <c r="D496" s="24" t="n"/>
+      <c r="E496" s="24" t="n"/>
+      <c r="F496" s="24" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B497" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="30" customHeight="1">
+      <c r="A498" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B498" s="28" t="inlineStr">
+        <is>
+          <t>On the student home, open AI Learning Tools → 🧠 Judgment Training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="30" customHeight="1">
+      <c r="A499" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B499" s="28" t="inlineStr">
+        <is>
+          <t>Read Here's the situation and pick one of A–D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="30" customHeight="1">
+      <c r="A500" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B500" s="28" t="inlineStr">
+        <is>
+          <t>In Why did you choose it?, write your reason. Your own language is fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="30" customHeight="1">
+      <c r="A501" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B501" s="28" t="inlineStr">
+        <is>
+          <t>Press Submit — the AI scores it and explains why another option may fit better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="30" customHeight="1">
+      <c r="A502" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B502" s="28" t="inlineStr">
+        <is>
+          <t>Tap 🏅 My Growth (top right) to see your judgment index and its 5 axes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="24" customHeight="1">
+      <c r="A503" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B503" s="30" t="inlineStr">
+        <is>
+          <t>Every option carries partial credit — only a clearly wrong choice scores low.</t>
+        </is>
+      </c>
+      <c r="C503" s="31" t="n"/>
+      <c r="D503" s="31" t="n"/>
+      <c r="E503" s="31" t="n"/>
+      <c r="F503" s="31" t="n"/>
+    </row>
+    <row r="504" ht="24" customHeight="1">
+      <c r="A504" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B504" s="30" t="inlineStr">
+        <is>
+          <t>The better you explain your reason, the higher the score — it trains thinking in words.</t>
+        </is>
+      </c>
+      <c r="C504" s="31" t="n"/>
+      <c r="D504" s="31" t="n"/>
+      <c r="E504" s="31" t="n"/>
+      <c r="F504" s="31" t="n"/>
+    </row>
+    <row r="505" ht="24" customHeight="1">
+      <c r="A505" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B505" s="30" t="inlineStr">
+        <is>
+          <t>Questions are linked to your textbook (e.g. Side by Side 2), so they stay in range.</t>
+        </is>
+      </c>
+      <c r="C505" s="31" t="n"/>
+      <c r="D505" s="31" t="n"/>
+      <c r="E505" s="31" t="n"/>
+      <c r="F505" s="31" t="n"/>
+    </row>
+    <row r="506" ht="24" customHeight="1">
+      <c r="A506" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B506" s="30" t="inlineStr">
+        <is>
+          <t>Each round comes from a different topic and angle, so questions never repeat.</t>
+        </is>
+      </c>
+      <c r="C506" s="31" t="n"/>
+      <c r="D506" s="31" t="n"/>
+      <c r="E506" s="31" t="n"/>
+      <c r="F506" s="31" t="n"/>
+    </row>
+    <row r="507" ht="26" customHeight="1">
+      <c r="A507" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · The AI needs a few seconds to write a question. The next one is prepared while you answer, so it usually appears instantly.</t>
+        </is>
+      </c>
+      <c r="B507" s="35" t="n"/>
+      <c r="C507" s="35" t="n"/>
+      <c r="D507" s="35" t="n"/>
+      <c r="E507" s="35" t="n"/>
+      <c r="F507" s="35" t="n"/>
+    </row>
+    <row r="508" ht="30" customHeight="1">
+      <c r="A508" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Getting it wrong is fine. Writing why you thought so is the whole point of this training.</t>
+        </is>
+      </c>
+      <c r="B508" s="33" t="n"/>
+      <c r="C508" s="33" t="n"/>
+      <c r="D508" s="33" t="n"/>
+      <c r="E508" s="33" t="n"/>
+      <c r="F508" s="33" t="n"/>
+    </row>
+    <row r="510" ht="26" customHeight="1">
+      <c r="A510" s="21" t="inlineStr">
+        <is>
+          <t>45  🍕 Grammar Pizza Master (word order)  —  Stack the toppings in sentence order</t>
+        </is>
+      </c>
+      <c r="B510" s="22" t="n"/>
+      <c r="C510" s="22" t="n"/>
+      <c r="D510" s="22" t="n"/>
+      <c r="E510" s="22" t="n"/>
+      <c r="F510" s="22" t="n"/>
+    </row>
+    <row r="511" ht="42" customHeight="1">
+      <c r="A511" s="23" t="inlineStr">
+        <is>
+          <t>📖 Words arrive as pizza toppings. Listen to the sentence first, then place the toppings in sentence order to finish the pizza. Subject, verb and object are colour-coded, so English word order sinks in visually.</t>
+        </is>
+      </c>
+      <c r="B511" s="24" t="n"/>
+      <c r="C511" s="24" t="n"/>
+      <c r="D511" s="24" t="n"/>
+      <c r="E511" s="24" t="n"/>
+      <c r="F511" s="24" t="n"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B512" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="30" customHeight="1">
+      <c r="A513" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B513" s="28" t="inlineStr">
+        <is>
+          <t>Open 🍕 Grammar Pizza Master in the games hub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="30" customHeight="1">
+      <c r="A514" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B514" s="28" t="inlineStr">
+        <is>
+          <t>Press Listen and start to hear the sentence first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="30" customHeight="1">
+      <c r="A515" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B515" s="28" t="inlineStr">
+        <is>
+          <t>Place the toppings below in sentence order onto the pizza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="30" customHeight="1">
+      <c r="A516" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B516" s="28" t="inlineStr">
+        <is>
+          <t>Stuck? Tap 💡 Hint! at the top right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="30" customHeight="1">
+      <c r="A517" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B517" s="28" t="inlineStr">
+        <is>
+          <t>Sentences grow longer from Level 1 → 2 → 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="24" customHeight="1">
+      <c r="A518" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B518" s="30" t="inlineStr">
+        <is>
+          <t>Each topping is labelled subject / verb / object, so word order becomes natural.</t>
+        </is>
+      </c>
+      <c r="C518" s="31" t="n"/>
+      <c r="D518" s="31" t="n"/>
+      <c r="E518" s="31" t="n"/>
+      <c r="F518" s="31" t="n"/>
+    </row>
+    <row r="519" ht="24" customHeight="1">
+      <c r="A519" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B519" s="30" t="inlineStr">
+        <is>
+          <t>If a textbook is assigned, sentences come from that book.</t>
+        </is>
+      </c>
+      <c r="C519" s="31" t="n"/>
+      <c r="D519" s="31" t="n"/>
+      <c r="E519" s="31" t="n"/>
+      <c r="F519" s="31" t="n"/>
+    </row>
+    <row r="520" ht="24" customHeight="1">
+      <c r="A520" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B520" s="30" t="inlineStr">
+        <is>
+          <t>A time limit keeps the drill fast and focused.</t>
+        </is>
+      </c>
+      <c r="C520" s="31" t="n"/>
+      <c r="D520" s="31" t="n"/>
+      <c r="E520" s="31" t="n"/>
+      <c r="F520" s="31" t="n"/>
+    </row>
+    <row r="521" ht="30" customHeight="1">
+      <c r="A521" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Read each word aloud as you place it — the order sticks far faster.</t>
+        </is>
+      </c>
+      <c r="B521" s="33" t="n"/>
+      <c r="C521" s="33" t="n"/>
+      <c r="D521" s="33" t="n"/>
+      <c r="E521" s="33" t="n"/>
+      <c r="F521" s="33" t="n"/>
+    </row>
+    <row r="523" ht="26" customHeight="1">
+      <c r="A523" s="21" t="inlineStr">
+        <is>
+          <t>46  🧱 Word Tetris  —  Stack word blocks and complete two lines</t>
+        </is>
+      </c>
+      <c r="B523" s="22" t="n"/>
+      <c r="C523" s="22" t="n"/>
+      <c r="D523" s="22" t="n"/>
+      <c r="E523" s="22" t="n"/>
+      <c r="F523" s="22" t="n"/>
+    </row>
+    <row r="524" ht="42" customHeight="1">
+      <c r="A524" s="23" t="inlineStr">
+        <is>
+          <t>📖 Classic Tetris with words on top. Words fall one at a time in sentence order — stack them well and clear a line to complete the sentence. Long words are wide blocks, short words are small ones; fitting them together makes the vocabulary stick.</t>
+        </is>
+      </c>
+      <c r="B524" s="24" t="n"/>
+      <c r="C524" s="24" t="n"/>
+      <c r="D524" s="24" t="n"/>
+      <c r="E524" s="24" t="n"/>
+      <c r="F524" s="24" t="n"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B525" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="30" customHeight="1">
+      <c r="A526" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B526" s="28" t="inlineStr">
+        <is>
+          <t>Open 🧱 Word Tetris in the games hub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="30" customHeight="1">
+      <c r="A527" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B527" s="28" t="inlineStr">
+        <is>
+          <t>Choose US English mode or CN Chinese mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="30" customHeight="1">
+      <c r="A528" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B528" s="28" t="inlineStr">
+        <is>
+          <t>Use ◀ ▶ to move, rotate, ▼ to speed up, ↓ to drop instantly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="30" customHeight="1">
+      <c r="A529" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B529" s="28" t="inlineStr">
+        <is>
+          <t>Each time a block lands you hear the word — repeat it aloud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530" ht="24" customHeight="1">
+      <c r="A530" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B530" s="30" t="inlineStr">
+        <is>
+          <t>English and Chinese modes play exactly the same way.</t>
+        </is>
+      </c>
+      <c r="C530" s="31" t="n"/>
+      <c r="D530" s="31" t="n"/>
+      <c r="E530" s="31" t="n"/>
+      <c r="F530" s="31" t="n"/>
+    </row>
+    <row r="531" ht="24" customHeight="1">
+      <c r="A531" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B531" s="30" t="inlineStr">
+        <is>
+          <t>Your high score is saved so you can beat it next time.</t>
+        </is>
+      </c>
+      <c r="C531" s="31" t="n"/>
+      <c r="D531" s="31" t="n"/>
+      <c r="E531" s="31" t="n"/>
+      <c r="F531" s="31" t="n"/>
+    </row>
+    <row r="532" ht="24" customHeight="1">
+      <c r="A532" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B532" s="30" t="inlineStr">
+        <is>
+          <t>Tidied up so nothing is cut off on a phone screen.</t>
+        </is>
+      </c>
+      <c r="C532" s="31" t="n"/>
+      <c r="D532" s="31" t="n"/>
+      <c r="E532" s="31" t="n"/>
+      <c r="F532" s="31" t="n"/>
+    </row>
+    <row r="533" ht="30" customHeight="1">
+      <c r="A533" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Lay the long words down low first — clearing lines gets much easier.</t>
+        </is>
+      </c>
+      <c r="B533" s="33" t="n"/>
+      <c r="C533" s="33" t="n"/>
+      <c r="D533" s="33" t="n"/>
+      <c r="E533" s="33" t="n"/>
+      <c r="F533" s="33" t="n"/>
+    </row>
+    <row r="535" ht="26" customHeight="1">
+      <c r="A535" s="21" t="inlineStr">
+        <is>
+          <t>47  🛡️ Tank Battle · Language Ace  —  Destroy in word order · action learning</t>
+        </is>
+      </c>
+      <c r="B535" s="22" t="n"/>
+      <c r="C535" s="22" t="n"/>
+      <c r="D535" s="22" t="n"/>
+      <c r="E535" s="22" t="n"/>
+      <c r="F535" s="22" t="n"/>
+    </row>
+    <row r="536" ht="42" customHeight="1">
+      <c r="A536" s="23" t="inlineStr">
+        <is>
+          <t>📖 Two new action-style learning games. In Tank Battle you destroy enemy tanks in the sentence's word order; in Language Ace you fly and answer as you go. Hands stay busy, so focus is high and repetition never feels dull.</t>
+        </is>
+      </c>
+      <c r="B536" s="24" t="n"/>
+      <c r="C536" s="24" t="n"/>
+      <c r="D536" s="24" t="n"/>
+      <c r="E536" s="24" t="n"/>
+      <c r="F536" s="24" t="n"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B537" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="30" customHeight="1">
+      <c r="A538" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B538" s="28" t="inlineStr">
+        <is>
+          <t>Open 🛡️ Tank Battle or ✈️ Language Ace in the games hub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539" ht="30" customHeight="1">
+      <c r="A539" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B539" s="28" t="inlineStr">
+        <is>
+          <t>For Tank Battle pick English / 中文, a battlefield (grass · desert · snow) and difficulty 1–7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="30" customHeight="1">
+      <c r="A540" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B540" s="28" t="inlineStr">
+        <is>
+          <t>Hold and drag the left button to move; short tap fires in that direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="30" customHeight="1">
+      <c r="A541" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B541" s="28" t="inlineStr">
+        <is>
+          <t>Destroy the tanks carrying the gold words of the sentence above, in order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="30" customHeight="1">
+      <c r="A542" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B542" s="28" t="inlineStr">
+        <is>
+          <t>Pick up jelly fuel cans to gain more time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="24" customHeight="1">
+      <c r="A543" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B543" s="30" t="inlineStr">
+        <is>
+          <t>Higher difficulty means faster enemies and faster speech — listening practice included.</t>
+        </is>
+      </c>
+      <c r="C543" s="31" t="n"/>
+      <c r="D543" s="31" t="n"/>
+      <c r="E543" s="31" t="n"/>
+      <c r="F543" s="31" t="n"/>
+    </row>
+    <row r="544" ht="24" customHeight="1">
+      <c r="A544" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B544" s="30" t="inlineStr">
+        <is>
+          <t>If a textbook is assigned, its sentences are used.</t>
+        </is>
+      </c>
+      <c r="C544" s="31" t="n"/>
+      <c r="D544" s="31" t="n"/>
+      <c r="E544" s="31" t="n"/>
+      <c r="F544" s="31" t="n"/>
+    </row>
+    <row r="545" ht="24" customHeight="1">
+      <c r="A545" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B545" s="30" t="inlineStr">
+        <is>
+          <t>Fully playable by touch on phones and tablets.</t>
+        </is>
+      </c>
+      <c r="C545" s="31" t="n"/>
+      <c r="D545" s="31" t="n"/>
+      <c r="E545" s="31" t="n"/>
+      <c r="F545" s="31" t="n"/>
+    </row>
+    <row r="546" ht="26" customHeight="1">
+      <c r="A546" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · These games are motion-heavy. On a slower device, lower the difficulty.</t>
+        </is>
+      </c>
+      <c r="B546" s="35" t="n"/>
+      <c r="C546" s="35" t="n"/>
+      <c r="D546" s="35" t="n"/>
+      <c r="E546" s="35" t="n"/>
+      <c r="F546" s="35" t="n"/>
+    </row>
+    <row r="547" ht="30" customHeight="1">
+      <c r="A547" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Games work best as review after the lesson, not before it.</t>
+        </is>
+      </c>
+      <c r="B547" s="33" t="n"/>
+      <c r="C547" s="33" t="n"/>
+      <c r="D547" s="33" t="n"/>
+      <c r="E547" s="33" t="n"/>
+      <c r="F547" s="33" t="n"/>
+    </row>
+    <row r="549" ht="26" customHeight="1">
+      <c r="A549" s="21" t="inlineStr">
+        <is>
+          <t>48  🔐 Log in with your face or fingerprint (passkey)  —  No password needed in the app</t>
+        </is>
+      </c>
+      <c r="B549" s="22" t="n"/>
+      <c r="C549" s="22" t="n"/>
+      <c r="D549" s="22" t="n"/>
+      <c r="E549" s="22" t="n"/>
+      <c r="F549" s="22" t="n"/>
+    </row>
+    <row r="550" ht="42" customHeight="1">
+      <c r="A550" s="23" t="inlineStr">
+        <is>
+          <t>📖 You can now log in with your face or fingerprint in the Mangoi Android app. Register once and you're in with a glance or a touch — no ID and password to type. Your secret never leaves your phone, so it's safer too.</t>
+        </is>
+      </c>
+      <c r="B550" s="24" t="n"/>
+      <c r="C550" s="24" t="n"/>
+      <c r="D550" s="24" t="n"/>
+      <c r="E550" s="24" t="n"/>
+      <c r="F550" s="24" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B551" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="552" ht="30" customHeight="1">
+      <c r="A552" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B552" s="28" t="inlineStr">
+        <is>
+          <t>Update the app to the latest version (v1.9 or later).</t>
+        </is>
+      </c>
+    </row>
+    <row r="553" ht="30" customHeight="1">
+      <c r="A553" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B553" s="28" t="inlineStr">
+        <is>
+          <t>Log in once with your ID and password as usual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="30" customHeight="1">
+      <c r="A554" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B554" s="28" t="inlineStr">
+        <is>
+          <t>When prompted, tap Register passkey and enrol your face or fingerprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555" ht="30" customHeight="1">
+      <c r="A555" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B555" s="28" t="inlineStr">
+        <is>
+          <t>From then on, log in with your face or fingerprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="24" customHeight="1">
+      <c r="A556" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B556" s="30" t="inlineStr">
+        <is>
+          <t>The credential stays only on your phone and is never sent to the server.</t>
+        </is>
+      </c>
+      <c r="C556" s="31" t="n"/>
+      <c r="D556" s="31" t="n"/>
+      <c r="E556" s="31" t="n"/>
+      <c r="F556" s="31" t="n"/>
+    </row>
+    <row r="557" ht="24" customHeight="1">
+      <c r="A557" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B557" s="30" t="inlineStr">
+        <is>
+          <t>Changed phones? Just register once more on the new device.</t>
+        </is>
+      </c>
+      <c r="C557" s="31" t="n"/>
+      <c r="D557" s="31" t="n"/>
+      <c r="E557" s="31" t="n"/>
+      <c r="F557" s="31" t="n"/>
+    </row>
+    <row r="558" ht="24" customHeight="1">
+      <c r="A558" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B558" s="30" t="inlineStr">
+        <is>
+          <t>Devices without passkey support keep working with the usual ID + password.</t>
+        </is>
+      </c>
+      <c r="C558" s="31" t="n"/>
+      <c r="D558" s="31" t="n"/>
+      <c r="E558" s="31" t="n"/>
+      <c r="F558" s="31" t="n"/>
+    </row>
+    <row r="559" ht="26" customHeight="1">
+      <c r="A559" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · This is an app-only feature. In a web browser, log in the usual way.</t>
+        </is>
+      </c>
+      <c r="B559" s="35" t="n"/>
+      <c r="C559" s="35" t="n"/>
+      <c r="D559" s="35" t="n"/>
+      <c r="E559" s="35" t="n"/>
+      <c r="F559" s="35" t="n"/>
+    </row>
+    <row r="560" ht="30" customHeight="1">
+      <c r="A560" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Younger students forget passwords constantly. Registering a passkey cuts those requests dramatically.</t>
+        </is>
+      </c>
+      <c r="B560" s="33" t="n"/>
+      <c r="C560" s="33" t="n"/>
+      <c r="D560" s="33" t="n"/>
+      <c r="E560" s="33" t="n"/>
+      <c r="F560" s="33" t="n"/>
+    </row>
+    <row r="562" ht="26" customHeight="1">
+      <c r="A562" s="21" t="inlineStr">
+        <is>
+          <t>49  🎤 Your speaking isn't cut off any more · a smarter AI friend  —  It waits even when you speak slowly</t>
+        </is>
+      </c>
+      <c r="B562" s="22" t="n"/>
+      <c r="C562" s="22" t="n"/>
+      <c r="D562" s="22" t="n"/>
+      <c r="E562" s="22" t="n"/>
+      <c r="F562" s="22" t="n"/>
+    </row>
+    <row r="563" ht="42" customHeight="1">
+      <c r="A563" s="23" t="inlineStr">
+        <is>
+          <t>📖 The microphone used to shut off while you were still thinking mid-sentence — that's fixed. The waiting time now adapts to the situation, and if your phone kills the microphone by itself it restarts automatically. The AI friend (Mango) no longer repeats itself, asks again when your speech is cut off, and actually slows down when you say “speak slowly”.</t>
+        </is>
+      </c>
+      <c r="B563" s="24" t="n"/>
+      <c r="C563" s="24" t="n"/>
+      <c r="D563" s="24" t="n"/>
+      <c r="E563" s="24" t="n"/>
+      <c r="F563" s="24" t="n"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B564" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="30" customHeight="1">
+      <c r="A565" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B565" s="28" t="inlineStr">
+        <is>
+          <t>Press the 🎤 button in Speech Coach, AI Warm-up or AI Friend and talk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="30" customHeight="1">
+      <c r="A566" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B566" s="28" t="inlineStr">
+        <is>
+          <t>Pausing to think is fine — it waits until you're really finished.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="30" customHeight="1">
+      <c r="A567" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B567" s="28" t="inlineStr">
+        <is>
+          <t>Say “Please speak slowly” to the AI friend and it will slow down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="30" customHeight="1">
+      <c r="A568" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B568" s="28" t="inlineStr">
+        <is>
+          <t>Choose the voice: male · female · alternating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="24" customHeight="1">
+      <c r="A569" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B569" s="30" t="inlineStr">
+        <is>
+          <t>Sudden microphone cut-outs on Android phones now recover automatically.</t>
+        </is>
+      </c>
+      <c r="C569" s="31" t="n"/>
+      <c r="D569" s="31" t="n"/>
+      <c r="E569" s="31" t="n"/>
+      <c r="F569" s="31" t="n"/>
+    </row>
+    <row r="570" ht="24" customHeight="1">
+      <c r="A570" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B570" s="30" t="inlineStr">
+        <is>
+          <t>The AI friend never repeats the same sentence.</t>
+        </is>
+      </c>
+      <c r="C570" s="31" t="n"/>
+      <c r="D570" s="31" t="n"/>
+      <c r="E570" s="31" t="n"/>
+      <c r="F570" s="31" t="n"/>
+    </row>
+    <row r="571" ht="24" customHeight="1">
+      <c r="A571" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B571" s="30" t="inlineStr">
+        <is>
+          <t>If your speech is clipped, the AI asks “Did you mean this?”</t>
+        </is>
+      </c>
+      <c r="C571" s="31" t="n"/>
+      <c r="D571" s="31" t="n"/>
+      <c r="E571" s="31" t="n"/>
+      <c r="F571" s="31" t="n"/>
+    </row>
+    <row r="572" ht="26" customHeight="1">
+      <c r="A572" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Noisy surroundings hurt recognition. Speak clearly in a quiet place.</t>
+        </is>
+      </c>
+      <c r="B572" s="35" t="n"/>
+      <c r="C572" s="35" t="n"/>
+      <c r="D572" s="35" t="n"/>
+      <c r="E572" s="35" t="n"/>
+      <c r="F572" s="35" t="n"/>
+    </row>
+    <row r="573" ht="30" customHeight="1">
+      <c r="A573" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Using an earphone microphone raises recognition accuracy noticeably.</t>
+        </is>
+      </c>
+      <c r="B573" s="33" t="n"/>
+      <c r="C573" s="33" t="n"/>
+      <c r="D573" s="33" t="n"/>
+      <c r="E573" s="33" t="n"/>
+      <c r="F573" s="33" t="n"/>
+    </row>
+    <row r="575" ht="26" customHeight="1">
+      <c r="A575" s="21" t="inlineStr">
+        <is>
+          <t>50  💳 Enrol and pay in one go  —  Pick teacher, days and time — lessons are scheduled automatically</t>
+        </is>
+      </c>
+      <c r="B575" s="22" t="n"/>
+      <c r="C575" s="22" t="n"/>
+      <c r="D575" s="22" t="n"/>
+      <c r="E575" s="22" t="n"/>
+      <c r="F575" s="22" t="n"/>
+    </row>
+    <row r="576" ht="42" customHeight="1">
+      <c r="A576" s="23" t="inlineStr">
+        <is>
+          <t>📖 You can now choose your teacher, days and time yourself and pay — and your whole schedule is created automatically. No more phoning after payment to arrange a timetable. If a slot already clashes with another lesson, you're told before you pay.</t>
+        </is>
+      </c>
+      <c r="B576" s="24" t="n"/>
+      <c r="C576" s="24" t="n"/>
+      <c r="D576" s="24" t="n"/>
+      <c r="E576" s="24" t="n"/>
+      <c r="F576" s="24" t="n"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B577" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="30" customHeight="1">
+      <c r="A578" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B578" s="28" t="inlineStr">
+        <is>
+          <t>Open the Enrolment screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="30" customHeight="1">
+      <c r="A579" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B579" s="28" t="inlineStr">
+        <is>
+          <t>① Choose a teacher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="30" customHeight="1">
+      <c r="A580" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B580" s="28" t="inlineStr">
+        <is>
+          <t>② Lesson options — times per week (1–5), term (1 / 3 / 6 / 12 months), length (20 or 40 min).</t>
+        </is>
+      </c>
+    </row>
+    <row r="581" ht="30" customHeight="1">
+      <c r="A581" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B581" s="28" t="inlineStr">
+        <is>
+          <t>③ Days &amp; time — pick as many days as your weekly count, then the start time and start date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582" ht="30" customHeight="1">
+      <c r="A582" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B582" s="28" t="inlineStr">
+        <is>
+          <t>When ✅ Available appears, press Pay at the bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583" ht="30" customHeight="1">
+      <c r="A583" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B583" s="28" t="inlineStr">
+        <is>
+          <t>Once payment completes, every session is created at once. Check it on My Page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="24" customHeight="1">
+      <c r="A584" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B584" s="30" t="inlineStr">
+        <is>
+          <t>Longer terms are cheaper — 6 months −5%, 12 months −10%.</t>
+        </is>
+      </c>
+      <c r="C584" s="31" t="n"/>
+      <c r="D584" s="31" t="n"/>
+      <c r="E584" s="31" t="n"/>
+      <c r="F584" s="31" t="n"/>
+    </row>
+    <row r="585" ht="24" customHeight="1">
+      <c r="A585" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B585" s="30" t="inlineStr">
+        <is>
+          <t>If the slot is taken, an ❌ appears so you can change it before paying.</t>
+        </is>
+      </c>
+      <c r="C585" s="31" t="n"/>
+      <c r="D585" s="31" t="n"/>
+      <c r="E585" s="31" t="n"/>
+      <c r="F585" s="31" t="n"/>
+    </row>
+    <row r="586" ht="24" customHeight="1">
+      <c r="A586" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B586" s="30" t="inlineStr">
+        <is>
+          <t>Postponing is free up to 30 minutes before the lesson; renewing extends the same day, time and teacher.</t>
+        </is>
+      </c>
+      <c r="C586" s="31" t="n"/>
+      <c r="D586" s="31" t="n"/>
+      <c r="E586" s="31" t="n"/>
+      <c r="F586" s="31" t="n"/>
+    </row>
+    <row r="587" ht="26" customHeight="1">
+      <c r="A587" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Lessons are created after payment is confirmed. Wait a moment right after paying and the schedule will appear.</t>
+        </is>
+      </c>
+      <c r="B587" s="35" t="n"/>
+      <c r="C587" s="35" t="n"/>
+      <c r="D587" s="35" t="n"/>
+      <c r="E587" s="35" t="n"/>
+      <c r="F587" s="35" t="n"/>
+    </row>
+    <row r="588" ht="30" customHeight="1">
+      <c r="A588" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Avoid days with school commitments. Choosing well up front beats rescheduling later.</t>
+        </is>
+      </c>
+      <c r="B588" s="33" t="n"/>
+      <c r="C588" s="33" t="n"/>
+      <c r="D588" s="33" t="n"/>
+      <c r="E588" s="33" t="n"/>
+      <c r="F588" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="450">
+  <mergeCells count="538">
     <mergeCell ref="A183:F183"/>
     <mergeCell ref="B209:F209"/>
     <mergeCell ref="B445:F445"/>
     <mergeCell ref="B301:F301"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B432:F432"/>
+    <mergeCell ref="B537:F537"/>
     <mergeCell ref="B276:F276"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B512:F512"/>
     <mergeCell ref="B238:F238"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B278:F278"/>
+    <mergeCell ref="B551:F551"/>
+    <mergeCell ref="B538:F538"/>
+    <mergeCell ref="B532:F532"/>
+    <mergeCell ref="B578:F578"/>
     <mergeCell ref="A274:F274"/>
     <mergeCell ref="A372:F372"/>
+    <mergeCell ref="B515:F515"/>
     <mergeCell ref="A107:F107"/>
     <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A549:F549"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B133:F133"/>
+    <mergeCell ref="A536:F536"/>
     <mergeCell ref="B369:F369"/>
     <mergeCell ref="B418:F418"/>
     <mergeCell ref="A315:F315"/>
@@ -7902,12 +9178,14 @@
     <mergeCell ref="B160:F160"/>
     <mergeCell ref="A486:F486"/>
     <mergeCell ref="B489:F489"/>
+    <mergeCell ref="B527:F527"/>
     <mergeCell ref="B368:F368"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B306:F306"/>
     <mergeCell ref="B433:F433"/>
     <mergeCell ref="A252:F252"/>
     <mergeCell ref="B227:F227"/>
+    <mergeCell ref="B531:F531"/>
     <mergeCell ref="B420:F420"/>
     <mergeCell ref="B199:F199"/>
     <mergeCell ref="B370:F370"/>
@@ -7915,6 +9193,7 @@
     <mergeCell ref="B291:F291"/>
     <mergeCell ref="A425:F425"/>
     <mergeCell ref="B228:F228"/>
+    <mergeCell ref="A562:F562"/>
     <mergeCell ref="A262:F262"/>
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="B148:F148"/>
@@ -7927,9 +9206,11 @@
     <mergeCell ref="B317:F317"/>
     <mergeCell ref="B217:F217"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B540:F540"/>
     <mergeCell ref="B319:F319"/>
     <mergeCell ref="B490:F490"/>
     <mergeCell ref="B383:F383"/>
+    <mergeCell ref="B554:F554"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A413:F413"/>
     <mergeCell ref="B439:F439"/>
@@ -7942,15 +9223,21 @@
     <mergeCell ref="B441:F441"/>
     <mergeCell ref="B161:F161"/>
     <mergeCell ref="B259:F259"/>
+    <mergeCell ref="B530:F530"/>
     <mergeCell ref="B136:F136"/>
+    <mergeCell ref="B505:F505"/>
+    <mergeCell ref="B499:F499"/>
     <mergeCell ref="B299:F299"/>
     <mergeCell ref="B225:F225"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B249:F249"/>
+    <mergeCell ref="A510:F510"/>
     <mergeCell ref="A295:F295"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="A334:F334"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A576:F576"/>
+    <mergeCell ref="A507:F507"/>
     <mergeCell ref="B91:F91"/>
     <mergeCell ref="B327:F327"/>
     <mergeCell ref="B454:F454"/>
@@ -7963,6 +9250,7 @@
     <mergeCell ref="B391:F391"/>
     <mergeCell ref="B247:F247"/>
     <mergeCell ref="B385:F385"/>
+    <mergeCell ref="B518:F518"/>
     <mergeCell ref="A302:F302"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="B151:F151"/>
@@ -7990,9 +9278,12 @@
     <mergeCell ref="B81:F81"/>
     <mergeCell ref="B366:F366"/>
     <mergeCell ref="B381:F381"/>
+    <mergeCell ref="B552:F552"/>
     <mergeCell ref="A386:F386"/>
+    <mergeCell ref="A508:F508"/>
     <mergeCell ref="B480:F480"/>
     <mergeCell ref="A373:F373"/>
+    <mergeCell ref="A573:F573"/>
     <mergeCell ref="B328:F328"/>
     <mergeCell ref="B455:F455"/>
     <mergeCell ref="A450:F450"/>
@@ -8001,13 +9292,17 @@
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B270:F270"/>
     <mergeCell ref="B392:F392"/>
+    <mergeCell ref="B568:F568"/>
     <mergeCell ref="B186:F186"/>
     <mergeCell ref="B457:F457"/>
     <mergeCell ref="B257:F257"/>
+    <mergeCell ref="B506:F506"/>
     <mergeCell ref="B288:F288"/>
+    <mergeCell ref="B555:F555"/>
     <mergeCell ref="B92:F92"/>
     <mergeCell ref="B394:F394"/>
     <mergeCell ref="A462:F462"/>
+    <mergeCell ref="B557:F557"/>
     <mergeCell ref="A399:F399"/>
     <mergeCell ref="A355:F355"/>
     <mergeCell ref="A305:F305"/>
@@ -8015,13 +9310,17 @@
     <mergeCell ref="A292:F292"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B185:F185"/>
+    <mergeCell ref="B581:F581"/>
     <mergeCell ref="A223:F223"/>
     <mergeCell ref="B475:F475"/>
     <mergeCell ref="A294:F294"/>
     <mergeCell ref="B176:F176"/>
     <mergeCell ref="B347:F347"/>
     <mergeCell ref="B341:F341"/>
+    <mergeCell ref="B583:F583"/>
     <mergeCell ref="B468:F468"/>
+    <mergeCell ref="B539:F539"/>
+    <mergeCell ref="B577:F577"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="A254:F254"/>
     <mergeCell ref="B405:F405"/>
@@ -8042,6 +9341,7 @@
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="A282:F282"/>
+    <mergeCell ref="B571:F571"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A242:F242"/>
     <mergeCell ref="B39:F39"/>
@@ -8065,6 +9365,7 @@
     <mergeCell ref="A402:F402"/>
     <mergeCell ref="B428:F428"/>
     <mergeCell ref="B415:F415"/>
+    <mergeCell ref="B586:F586"/>
     <mergeCell ref="A168:F168"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B123:F123"/>
@@ -8072,10 +9373,13 @@
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B286:F286"/>
     <mergeCell ref="B479:F479"/>
+    <mergeCell ref="B584:F584"/>
+    <mergeCell ref="A547:F547"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A255:F255"/>
     <mergeCell ref="A364:F364"/>
     <mergeCell ref="A192:F192"/>
+    <mergeCell ref="B504:F504"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B248:F248"/>
@@ -8083,24 +9387,29 @@
     <mergeCell ref="B235:F235"/>
     <mergeCell ref="A96:F96"/>
     <mergeCell ref="B337:F337"/>
+    <mergeCell ref="B579:F579"/>
     <mergeCell ref="B103:F103"/>
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="B205:F205"/>
     <mergeCell ref="B339:F339"/>
     <mergeCell ref="A352:F352"/>
+    <mergeCell ref="B501:F501"/>
     <mergeCell ref="A485:F485"/>
+    <mergeCell ref="B526:F526"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A410:F410"/>
     <mergeCell ref="B194:F194"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="A118:F118"/>
     <mergeCell ref="B492:F492"/>
+    <mergeCell ref="B528:F528"/>
     <mergeCell ref="A474:F474"/>
     <mergeCell ref="B131:F131"/>
     <mergeCell ref="B236:F236"/>
     <mergeCell ref="B307:F307"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B429:F429"/>
+    <mergeCell ref="B500:F500"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B465:F465"/>
     <mergeCell ref="B350:F350"/>
@@ -8109,11 +9418,14 @@
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B287:F287"/>
     <mergeCell ref="B358:F358"/>
+    <mergeCell ref="B529:F529"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="A265:F265"/>
+    <mergeCell ref="A563:F563"/>
     <mergeCell ref="B289:F289"/>
     <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A550:F550"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A202:F202"/>
     <mergeCell ref="B241:F241"/>
@@ -8128,16 +9440,19 @@
     <mergeCell ref="A447:F447"/>
     <mergeCell ref="A434:F434"/>
     <mergeCell ref="B219:F219"/>
+    <mergeCell ref="B517:F517"/>
     <mergeCell ref="A213:F213"/>
     <mergeCell ref="B210:F210"/>
     <mergeCell ref="A449:F449"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A424:F424"/>
+    <mergeCell ref="A495:F495"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B318:F318"/>
     <mergeCell ref="A482:F482"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B520:F520"/>
     <mergeCell ref="B308:F308"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B397:F397"/>
@@ -8149,31 +9464,43 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B361:F361"/>
+    <mergeCell ref="A572:F572"/>
     <mergeCell ref="A493:F493"/>
     <mergeCell ref="B150:F150"/>
     <mergeCell ref="B321:F321"/>
     <mergeCell ref="B215:F215"/>
     <mergeCell ref="A139:F139"/>
     <mergeCell ref="A272:F272"/>
+    <mergeCell ref="B513:F513"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B152:F152"/>
     <mergeCell ref="A203:F203"/>
+    <mergeCell ref="B542:F542"/>
     <mergeCell ref="B229:F229"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="A140:F140"/>
+    <mergeCell ref="B514:F514"/>
     <mergeCell ref="B452:F452"/>
+    <mergeCell ref="B544:F544"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="B258:F258"/>
     <mergeCell ref="B147:F147"/>
     <mergeCell ref="B451:F451"/>
+    <mergeCell ref="B543:F543"/>
     <mergeCell ref="B481:F481"/>
     <mergeCell ref="B456:F456"/>
     <mergeCell ref="B260:F260"/>
+    <mergeCell ref="A521:F521"/>
+    <mergeCell ref="B545:F545"/>
+    <mergeCell ref="A496:F496"/>
     <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A523:F523"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B163:F163"/>
+    <mergeCell ref="A560:F560"/>
     <mergeCell ref="A354:F354"/>
+    <mergeCell ref="B570:F570"/>
     <mergeCell ref="B138:F138"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B309:F309"/>
@@ -8198,12 +9525,17 @@
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="A275:F275"/>
     <mergeCell ref="B316:F316"/>
+    <mergeCell ref="B565:F565"/>
+    <mergeCell ref="A511:F511"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B266:F266"/>
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="B393:F393"/>
     <mergeCell ref="B331:F331"/>
     <mergeCell ref="B453:F453"/>
+    <mergeCell ref="B502:F502"/>
+    <mergeCell ref="B558:F558"/>
+    <mergeCell ref="B564:F564"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B197:F197"/>
@@ -8211,13 +9543,18 @@
     <mergeCell ref="B268:F268"/>
     <mergeCell ref="B153:F153"/>
     <mergeCell ref="B395:F395"/>
+    <mergeCell ref="B566:F566"/>
+    <mergeCell ref="B553:F553"/>
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B261:F261"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="B184:F184"/>
+    <mergeCell ref="A587:F587"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A524:F524"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A224:F224"/>
+    <mergeCell ref="A588:F588"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="B250:F250"/>
     <mergeCell ref="B166:F166"/>
@@ -8235,9 +9572,13 @@
     <mergeCell ref="B281:F281"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B256:F256"/>
+    <mergeCell ref="B497:F497"/>
+    <mergeCell ref="B541:F541"/>
+    <mergeCell ref="A535:F535"/>
     <mergeCell ref="A473:F473"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A575:F575"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="B121:F121"/>
@@ -8245,20 +9586,25 @@
     <mergeCell ref="A285:F285"/>
     <mergeCell ref="B357:F357"/>
     <mergeCell ref="B167:F167"/>
+    <mergeCell ref="B503:F503"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="B111:F111"/>
     <mergeCell ref="B421:F421"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B396:F396"/>
+    <mergeCell ref="B567:F567"/>
     <mergeCell ref="B175:F175"/>
     <mergeCell ref="B162:F162"/>
     <mergeCell ref="B267:F267"/>
     <mergeCell ref="B398:F398"/>
+    <mergeCell ref="B569:F569"/>
+    <mergeCell ref="B525:F525"/>
     <mergeCell ref="B269:F269"/>
     <mergeCell ref="A403:F403"/>
     <mergeCell ref="B187:F187"/>
     <mergeCell ref="A182:F182"/>
     <mergeCell ref="A304:F304"/>
+    <mergeCell ref="B556:F556"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="A461:F461"/>
     <mergeCell ref="B251:F251"/>
@@ -8267,21 +9613,25 @@
     <mergeCell ref="B216:F216"/>
     <mergeCell ref="B487:F487"/>
     <mergeCell ref="B414:F414"/>
+    <mergeCell ref="B585:F585"/>
     <mergeCell ref="B188:F188"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="B280:F280"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B218:F218"/>
     <mergeCell ref="B351:F351"/>
+    <mergeCell ref="B516:F516"/>
     <mergeCell ref="B416:F416"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B488:F488"/>
     <mergeCell ref="A179:F179"/>
     <mergeCell ref="B409:F409"/>
+    <mergeCell ref="B580:F580"/>
     <mergeCell ref="A322:F322"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B346:F346"/>
+    <mergeCell ref="B582:F582"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A324:F324"/>
     <mergeCell ref="A180:F180"/>
@@ -8296,12 +9646,14 @@
     <mergeCell ref="B164:F164"/>
     <mergeCell ref="B406:F406"/>
     <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B498:F498"/>
     <mergeCell ref="B206:F206"/>
     <mergeCell ref="A233:F233"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="B326:F326"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="B130:F130"/>
+    <mergeCell ref="A533:F533"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A312:F312"/>
     <mergeCell ref="A483:F483"/>
@@ -8321,8 +9673,11 @@
     <mergeCell ref="B427:F427"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B348:F348"/>
+    <mergeCell ref="B519:F519"/>
     <mergeCell ref="B419:F419"/>
     <mergeCell ref="B298:F298"/>
+    <mergeCell ref="A559:F559"/>
+    <mergeCell ref="A546:F546"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="A325:F325"/>
     <mergeCell ref="B51:F51"/>
